--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/18062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/18062026.xlsx
@@ -1,117 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jueves, 18 de junio de 2026
-*Evangelio del Día*
-Lectura del santo evangelio según san Mateo
-Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
-*Oración de la mañana*
-Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
-Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
-Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
-En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,193 +456,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>jueves, 18 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 7-15 En aquel tiempo, Jesús dijo a sus discípulos: “Cuando ustedes hagan oración, no hablen mucho, como los paganos, que se imaginan que a fuerza de mucho hablar serán escuchados. No los imiten, porque el Padre sabe lo que les hace falta, antes de que se lo pidan. Ustedes pues, oren así: Padre nuestro, que estás en el cielo, santificado sea tu nombre, venga tu Reino, hágase tu voluntad en la tierra como en el cielo. Danos hoy nuestro pan de cada día, perdona nuestras ofensas, como también nosotros perdonamos a los que nos ofenden; no nos dejes caer en tentación y líbranos del mal. Si ustedes perdonan las faltas a los hombres, también a ustedes los perdonará el Padre celestial. Pero si ustedes no perdonan a los hombres, tampoco el Padre les perdonará a ustedes sus faltas”.
+*Oración de la mañana*
+Querido Jesús, me presento ante ti en humildad y silencio, reconociendo que no son las palabras abundantes sino la sinceridad del corazón con la que te busco. Ayúdame a recordar que la oración no es tanto el hablar, sino más bien el escuchar y el estar en tu presencia.
+Amado Padre, te agradezco por este nuevo día que me ofreces. Gracias por conocer mis necesidades incluso antes de que las exprese. Que se haga tu voluntad en mi vida, así como es en el cielo. Dame el pan de cada día, no solo físico, sino el espiritual que me alimenta en el camino de la fe. Ayúdame a perdonar a los demás, como tú me has perdonado.
+Espíritu Santo, dulce huésped del alma, te pido que me guíes en este día. Llena mi corazón con tu sabiduría y fortaleza para resistir las tentaciones y los males que puedan surgir. Inspírame a vivir con amor y a perdonar, así como soy perdonado.
+En la trinidad sagrada, deposito mi fe y mi esperanza. Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>